--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122154532</v>
+        <v>135965550</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480796</v>
+        <v>480813</v>
       </c>
       <c r="R2" t="n">
-        <v>6950471</v>
+        <v>6950447</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,49 +765,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154532</t>
+          <t>https://artportalen.se/Sighting/135965550</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122154535</v>
+        <v>122154532</v>
       </c>
       <c r="B3" t="n">
-        <v>97983</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480780</v>
+        <v>480796</v>
       </c>
       <c r="R3" t="n">
-        <v>6950487</v>
+        <v>6950471</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,16 +878,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154535</t>
+          <t>https://artportalen.se/Sighting/122154532</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122154531</v>
+        <v>135966393</v>
       </c>
       <c r="B4" t="n">
-        <v>79085</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480881</v>
+        <v>480750</v>
       </c>
       <c r="R4" t="n">
-        <v>6950352</v>
+        <v>6950504</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +969,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154531</t>
+          <t>https://artportalen.se/Sighting/135966393</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122154530</v>
+        <v>135966486</v>
       </c>
       <c r="B5" t="n">
-        <v>79917</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480879</v>
+        <v>480709</v>
       </c>
       <c r="R5" t="n">
-        <v>6950354</v>
+        <v>6950560</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154530</t>
+          <t>https://artportalen.se/Sighting/135966486</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122154533</v>
+        <v>135966978</v>
       </c>
       <c r="B6" t="n">
-        <v>92329</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480796</v>
+        <v>480694</v>
       </c>
       <c r="R6" t="n">
-        <v>6950466</v>
+        <v>6950616</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,16 +1173,1556 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135966978</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135967170</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92050</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>480697</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6950617</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135967170</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135967509</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92050</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>480747</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6950566</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135967509</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135967578</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92050</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>480750</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6950555</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135967578</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135964610</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>480859</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6950376</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135964610</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135966354</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>480747</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6950494</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135966354</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135966883</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>480689</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6950597</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135966883</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135967194</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>480694</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6950627</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135967194</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135965221</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>480853</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6950411</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135965221</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135968104</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>480848</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6950450</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135968104</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135964484</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>480901</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6950385</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135964484</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135966337</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>480775</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6950503</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135966337</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122154535</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>480780</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6950487</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154535</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122154531</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>480881</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6950352</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154531</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122154530</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>480879</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6950354</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154530</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122154533</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>480796</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6950466</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122154533</t>
         </is>
@@ -1195,6 +2735,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135965550</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122154532</v>
+        <v>136094355</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>83422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>480796</v>
       </c>
       <c r="R3" t="n">
-        <v>6950471</v>
+        <v>6950556</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154532</t>
+          <t>https://artportalen.se/Sighting/136094355</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135966393</v>
+        <v>136094842</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480750</v>
+        <v>480724</v>
       </c>
       <c r="R4" t="n">
-        <v>6950504</v>
+        <v>6950517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,16 +980,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135966393</t>
+          <t>https://artportalen.se/Sighting/136094842</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135966486</v>
+        <v>122154532</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480709</v>
+        <v>480796</v>
       </c>
       <c r="R5" t="n">
-        <v>6950560</v>
+        <v>6950471</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135966486</t>
+          <t>https://artportalen.se/Sighting/122154532</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135966978</v>
+        <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480694</v>
+        <v>480750</v>
       </c>
       <c r="R6" t="n">
-        <v>6950616</v>
+        <v>6950504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135966978</t>
+          <t>https://artportalen.se/Sighting/135966393</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135967170</v>
+        <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480697</v>
+        <v>480709</v>
       </c>
       <c r="R7" t="n">
-        <v>6950617</v>
+        <v>6950560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,16 +1286,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135967170</t>
+          <t>https://artportalen.se/Sighting/135966486</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135967509</v>
+        <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480747</v>
+        <v>480694</v>
       </c>
       <c r="R8" t="n">
-        <v>6950566</v>
+        <v>6950616</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135967509</t>
+          <t>https://artportalen.se/Sighting/135966978</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135967578</v>
+        <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480750</v>
+        <v>480697</v>
       </c>
       <c r="R9" t="n">
-        <v>6950555</v>
+        <v>6950617</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,54 +1490,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135967578</t>
+          <t>https://artportalen.se/Sighting/135967170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135964610</v>
+        <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480859</v>
+        <v>480747</v>
       </c>
       <c r="R10" t="n">
-        <v>6950376</v>
+        <v>6950566</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1592,38 +1592,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135964610</t>
+          <t>https://artportalen.se/Sighting/135967509</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135966354</v>
+        <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480747</v>
+        <v>480750</v>
       </c>
       <c r="R11" t="n">
-        <v>6950494</v>
+        <v>6950555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,51 +1694,47 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135966354</t>
+          <t>https://artportalen.se/Sighting/135967578</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135966883</v>
+        <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>92457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4877</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Leptoporus mollis/erubescens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480689</v>
+        <v>480774</v>
       </c>
       <c r="R12" t="n">
-        <v>6950597</v>
+        <v>6950469</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,12 +1761,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,16 +1792,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135966883</t>
+          <t>https://artportalen.se/Sighting/136095456</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135967194</v>
+        <v>135964610</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,14 +1829,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480694</v>
+        <v>480859</v>
       </c>
       <c r="R13" t="n">
-        <v>6950627</v>
+        <v>6950376</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,51 +1894,51 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135967194</t>
+          <t>https://artportalen.se/Sighting/135964610</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135965221</v>
+        <v>135966354</v>
       </c>
       <c r="B14" t="n">
-        <v>83428</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480853</v>
+        <v>480747</v>
       </c>
       <c r="R14" t="n">
-        <v>6950411</v>
+        <v>6950494</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,51 +1996,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135965221</t>
+          <t>https://artportalen.se/Sighting/135966354</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135968104</v>
+        <v>135966883</v>
       </c>
       <c r="B15" t="n">
-        <v>80560</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480848</v>
+        <v>480689</v>
       </c>
       <c r="R15" t="n">
-        <v>6950450</v>
+        <v>6950597</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,56 +2098,51 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135968104</t>
+          <t>https://artportalen.se/Sighting/135966883</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135964484</v>
+        <v>135967194</v>
       </c>
       <c r="B16" t="n">
-        <v>57167</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480901</v>
+        <v>480694</v>
       </c>
       <c r="R16" t="n">
-        <v>6950385</v>
+        <v>6950627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,59 +2200,54 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135964484</t>
+          <t>https://artportalen.se/Sighting/135967194</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135966337</v>
+        <v>136093670</v>
       </c>
       <c r="B17" t="n">
-        <v>58141</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480775</v>
+        <v>480837</v>
       </c>
       <c r="R17" t="n">
-        <v>6950503</v>
+        <v>6950459</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2285,12 +2271,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,54 +2302,54 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135966337</t>
+          <t>https://artportalen.se/Sighting/136093670</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122154535</v>
+        <v>136093757</v>
       </c>
       <c r="B18" t="n">
-        <v>97983</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480780</v>
+        <v>480835</v>
       </c>
       <c r="R18" t="n">
-        <v>6950487</v>
+        <v>6950510</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2387,12 +2373,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,65 +2403,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154535</t>
+          <t>https://artportalen.se/Sighting/136093757</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154531</v>
+        <v>136093848</v>
       </c>
       <c r="B19" t="n">
-        <v>79085</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480881</v>
+        <v>480827</v>
       </c>
       <c r="R19" t="n">
-        <v>6950352</v>
+        <v>6950529</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2489,12 +2485,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,65 +2515,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154531</t>
+          <t>https://artportalen.se/Sighting/136093848</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154530</v>
+        <v>136093916</v>
       </c>
       <c r="B20" t="n">
-        <v>79917</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480879</v>
+        <v>480801</v>
       </c>
       <c r="R20" t="n">
-        <v>6950354</v>
+        <v>6950547</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2591,12 +2597,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2611,65 +2627,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154530</t>
+          <t>https://artportalen.se/Sighting/136093916</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154533</v>
+        <v>136094182</v>
       </c>
       <c r="B21" t="n">
-        <v>92329</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480796</v>
+        <v>480795</v>
       </c>
       <c r="R21" t="n">
-        <v>6950466</v>
+        <v>6950548</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2693,12 +2709,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2713,16 +2739,1182 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136094182</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136094627</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>480706</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6950573</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136094627</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135965221</v>
+      </c>
+      <c r="B23" t="n">
+        <v>83430</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>480853</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6950411</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135965221</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135968104</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80562</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>480848</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6950450</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135968104</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135964484</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>480901</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6950385</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135964484</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135966337</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>480775</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6950503</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135966337</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136094694</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>480706</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6950573</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136094694</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122154535</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>480780</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6950487</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154535</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136094110</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98155</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>480795</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6950548</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136094110</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122154531</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>480881</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6950352</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154531</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122154530</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>480879</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6950354</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154530</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122154533</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>480796</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6950466</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122154533</t>
         </is>
@@ -2750,6 +3942,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135965550</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136094355</v>
       </c>
       <c r="B3" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136094842</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92457</v>
+        <v>92458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135964610</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>135966354</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135966883</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135967194</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136093670</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136093757</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136093848</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136093916</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136094182</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136094627</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135965221</v>
       </c>
       <c r="B23" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>135968104</v>
       </c>
       <c r="B24" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135965550</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136094355</v>
       </c>
       <c r="B3" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136094842</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92459</v>
+        <v>92460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135964610</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>135966354</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135966883</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135967194</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136093670</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136093757</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136093848</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136093916</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136094182</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136094627</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135965221</v>
       </c>
       <c r="B23" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>135968104</v>
       </c>
       <c r="B24" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>135964484</v>
       </c>
       <c r="B25" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135966337</v>
       </c>
       <c r="B26" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135965550</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136094355</v>
       </c>
       <c r="B3" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136094842</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92460</v>
+        <v>92466</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135964610</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>135966354</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135966883</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135967194</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136093670</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136093757</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136093848</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136093916</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136094182</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136094627</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135965221</v>
       </c>
       <c r="B23" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>135968104</v>
       </c>
       <c r="B24" t="n">
-        <v>80564</v>
+        <v>80568</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>135964484</v>
       </c>
       <c r="B25" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135966337</v>
       </c>
       <c r="B26" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135965550</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136094355</v>
       </c>
       <c r="B3" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136094842</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92466</v>
+        <v>92467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135964610</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>135966354</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135966883</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135967194</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136093670</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136093757</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136093848</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136093916</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136094182</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136094627</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135965221</v>
       </c>
       <c r="B23" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>135968104</v>
       </c>
       <c r="B24" t="n">
-        <v>80568</v>
+        <v>80569</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>135964484</v>
       </c>
       <c r="B25" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135966337</v>
       </c>
       <c r="B26" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135965550</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136094355</v>
       </c>
       <c r="B3" t="n">
-        <v>83429</v>
+        <v>83433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136094842</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92467</v>
+        <v>92473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135964610</v>
       </c>
       <c r="B13" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>135966354</v>
       </c>
       <c r="B14" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135966883</v>
       </c>
       <c r="B15" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135967194</v>
       </c>
       <c r="B16" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136093670</v>
       </c>
       <c r="B17" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136093757</v>
       </c>
       <c r="B18" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136093848</v>
       </c>
       <c r="B19" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136093916</v>
       </c>
       <c r="B20" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136094182</v>
       </c>
       <c r="B21" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136094627</v>
       </c>
       <c r="B22" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135965221</v>
       </c>
       <c r="B23" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>135968104</v>
       </c>
       <c r="B24" t="n">
-        <v>80569</v>
+        <v>80573</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135965550</v>
       </c>
       <c r="B2" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136094355</v>
       </c>
       <c r="B3" t="n">
-        <v>83433</v>
+        <v>83439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136094842</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92473</v>
+        <v>92480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135964610</v>
       </c>
       <c r="B13" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>135966354</v>
       </c>
       <c r="B14" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135966883</v>
       </c>
       <c r="B15" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135967194</v>
       </c>
       <c r="B16" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136093670</v>
       </c>
       <c r="B17" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136093757</v>
       </c>
       <c r="B18" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136093848</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136093916</v>
       </c>
       <c r="B20" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136094182</v>
       </c>
       <c r="B21" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136094627</v>
       </c>
       <c r="B22" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135965221</v>
       </c>
       <c r="B23" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>135968104</v>
       </c>
       <c r="B24" t="n">
-        <v>80573</v>
+        <v>80579</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>135964484</v>
       </c>
       <c r="B25" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135966337</v>
       </c>
       <c r="B26" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92480</v>
+        <v>92481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135965550</v>
       </c>
       <c r="B2" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136094355</v>
       </c>
       <c r="B3" t="n">
-        <v>83439</v>
+        <v>83452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136094842</v>
       </c>
       <c r="B4" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92481</v>
+        <v>92494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135964610</v>
       </c>
       <c r="B13" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>135966354</v>
       </c>
       <c r="B14" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135966883</v>
       </c>
       <c r="B15" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135967194</v>
       </c>
       <c r="B16" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136093670</v>
       </c>
       <c r="B17" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136093757</v>
       </c>
       <c r="B18" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136093848</v>
       </c>
       <c r="B19" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136093916</v>
       </c>
       <c r="B20" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136094182</v>
       </c>
       <c r="B21" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136094627</v>
       </c>
       <c r="B22" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135965221</v>
       </c>
       <c r="B23" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>135968104</v>
       </c>
       <c r="B24" t="n">
-        <v>80579</v>
+        <v>80592</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>135964484</v>
       </c>
       <c r="B25" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135966337</v>
       </c>
       <c r="B26" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135965550</v>
       </c>
       <c r="B2" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136094355</v>
       </c>
       <c r="B3" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136094842</v>
       </c>
       <c r="B4" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135966393</v>
       </c>
       <c r="B6" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135966486</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135966978</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135967170</v>
       </c>
       <c r="B9" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135967509</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135967578</v>
       </c>
       <c r="B11" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135964610</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>135966354</v>
       </c>
       <c r="B14" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135966883</v>
       </c>
       <c r="B15" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135967194</v>
       </c>
       <c r="B16" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136093670</v>
       </c>
       <c r="B17" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136093757</v>
       </c>
       <c r="B18" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136093848</v>
       </c>
       <c r="B19" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136093916</v>
       </c>
       <c r="B20" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136094182</v>
       </c>
       <c r="B21" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136094627</v>
       </c>
       <c r="B22" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135965221</v>
       </c>
       <c r="B23" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>135968104</v>
       </c>
       <c r="B24" t="n">
-        <v>80592</v>
+        <v>80593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
